--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252454</v>
+        <v>123252628</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>90972</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478458</v>
+        <v>478423</v>
       </c>
       <c r="R2" t="n">
-        <v>7013736</v>
+        <v>7013572</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252628</v>
+        <v>123252454</v>
       </c>
       <c r="B3" t="n">
-        <v>90972</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478423</v>
+        <v>478458</v>
       </c>
       <c r="R3" t="n">
-        <v>7013572</v>
+        <v>7013736</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,21 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -807,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252454</v>
+        <v>123252179</v>
       </c>
       <c r="B3" t="n">
         <v>74863</v>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478458</v>
+        <v>478476</v>
       </c>
       <c r="R3" t="n">
-        <v>7013736</v>
+        <v>7013856</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -908,6 +908,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252179</v>
+        <v>123252454</v>
       </c>
       <c r="B4" t="n">
         <v>74863</v>
@@ -964,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478476</v>
+        <v>478458</v>
       </c>
       <c r="R4" t="n">
-        <v>7013856</v>
+        <v>7013736</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1025,21 +1040,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252628</v>
+        <v>123252179</v>
       </c>
       <c r="B2" t="n">
-        <v>90972</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478423</v>
+        <v>478476</v>
       </c>
       <c r="R2" t="n">
-        <v>7013572</v>
+        <v>7013856</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252179</v>
+        <v>123252628</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>90975</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478476</v>
+        <v>478423</v>
       </c>
       <c r="R3" t="n">
-        <v>7013856</v>
+        <v>7013572</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +911,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,7 +942,7 @@
         <v>123252454</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>123252628</v>
       </c>
       <c r="B3" t="n">
-        <v>90975</v>
+        <v>90977</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>123252628</v>
       </c>
       <c r="B3" t="n">
-        <v>90977</v>
+        <v>90983</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123252179</v>
       </c>
       <c r="B2" t="n">
-        <v>74866</v>
+        <v>74869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252628</v>
+        <v>123252454</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>74869</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478423</v>
+        <v>478458</v>
       </c>
       <c r="R3" t="n">
-        <v>7013572</v>
+        <v>7013736</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,21 +908,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -939,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252454</v>
+        <v>123252628</v>
       </c>
       <c r="B4" t="n">
-        <v>74866</v>
+        <v>90986</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478458</v>
+        <v>478423</v>
       </c>
       <c r="R4" t="n">
-        <v>7013736</v>
+        <v>7013572</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252179</v>
+        <v>123252628</v>
       </c>
       <c r="B2" t="n">
-        <v>74869</v>
+        <v>91003</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478476</v>
+        <v>478423</v>
       </c>
       <c r="R2" t="n">
-        <v>7013856</v>
+        <v>7013572</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,7 +810,7 @@
         <v>123252454</v>
       </c>
       <c r="B3" t="n">
-        <v>74869</v>
+        <v>74875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252628</v>
+        <v>123252179</v>
       </c>
       <c r="B4" t="n">
-        <v>90986</v>
+        <v>74875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478423</v>
+        <v>478476</v>
       </c>
       <c r="R4" t="n">
-        <v>7013572</v>
+        <v>7013856</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252628</v>
+        <v>123252179</v>
       </c>
       <c r="B2" t="n">
-        <v>91003</v>
+        <v>74878</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478423</v>
+        <v>478476</v>
       </c>
       <c r="R2" t="n">
-        <v>7013572</v>
+        <v>7013856</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,7 +810,7 @@
         <v>123252454</v>
       </c>
       <c r="B3" t="n">
-        <v>74875</v>
+        <v>74878</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252179</v>
+        <v>123252628</v>
       </c>
       <c r="B4" t="n">
-        <v>74875</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478476</v>
+        <v>478423</v>
       </c>
       <c r="R4" t="n">
-        <v>7013856</v>
+        <v>7013572</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123252179</v>
       </c>
       <c r="B2" t="n">
-        <v>74878</v>
+        <v>74879</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>123252454</v>
       </c>
       <c r="B3" t="n">
-        <v>74878</v>
+        <v>74879</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>123252628</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252179</v>
+        <v>123252454</v>
       </c>
       <c r="B2" t="n">
         <v>74879</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478476</v>
+        <v>478458</v>
       </c>
       <c r="R2" t="n">
-        <v>7013856</v>
+        <v>7013736</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -776,21 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -807,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123252454</v>
+        <v>123252628</v>
       </c>
       <c r="B3" t="n">
-        <v>74879</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478458</v>
+        <v>478423</v>
       </c>
       <c r="R3" t="n">
-        <v>7013736</v>
+        <v>7013572</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i äldre granskog</t>
+          <t>På gammal tall i äldre granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +893,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252628</v>
+        <v>123252179</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>74879</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478423</v>
+        <v>478476</v>
       </c>
       <c r="R4" t="n">
-        <v>7013572</v>
+        <v>7013856</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal tall i äldre granskog</t>
+          <t>På bark på stam av levande gammal gran i äldre granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123252454</v>
+        <v>123252179</v>
       </c>
       <c r="B2" t="n">
         <v>74879</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478458</v>
+        <v>478476</v>
       </c>
       <c r="R2" t="n">
-        <v>7013736</v>
+        <v>7013856</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -776,6 +776,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -924,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123252179</v>
+        <v>123252454</v>
       </c>
       <c r="B4" t="n">
         <v>74879</v>
@@ -964,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478476</v>
+        <v>478458</v>
       </c>
       <c r="R4" t="n">
-        <v>7013856</v>
+        <v>7013736</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1025,21 +1040,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 53023-2019 artfynd.xlsx
+++ b/artfynd/A 53023-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126499044</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100543</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ås, Ås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478507</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7013771</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Noro-Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
